--- a/product-definitions/spreadsheet/soil.xlsx
+++ b/product-definitions/spreadsheet/soil.xlsx
@@ -172,7 +172,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -198,14 +198,9 @@
     <font>
       <color theme="1"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <color theme="1"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -223,7 +218,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -244,24 +239,23 @@
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1574,7 +1568,7 @@
       <c r="B3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="7" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1614,7 +1608,7 @@
       <c r="B8" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="8">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -1622,7 +1616,7 @@
       <c r="B9" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="9" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1630,7 +1624,7 @@
       <c r="B10" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="9" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1659,7 +1653,7 @@
       <c r="B15" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="7" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1699,27 +1693,27 @@
       <c r="B20" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="9">
+      <c r="C20" s="8">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="15.75" customHeight="1">
       <c r="B21" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="9" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="15.75" customHeight="1">
       <c r="B22" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="9" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="15.75" customHeight="1">
       <c r="B23" s="7" t="s">
         <v>24</v>
       </c>
@@ -1727,7 +1721,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="15.75" customHeight="1">
       <c r="B24" s="7" t="s">
         <v>26</v>
       </c>
@@ -1735,20 +1729,21 @@
         <v>27</v>
       </c>
     </row>
-    <row r="26">
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="15.75" customHeight="1">
       <c r="B27" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="15.75" customHeight="1">
       <c r="B28" s="7" t="s">
         <v>14</v>
       </c>
@@ -1756,7 +1751,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="15.75" customHeight="1">
       <c r="B29" s="7" t="s">
         <v>2</v>
       </c>
@@ -1764,7 +1759,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="15.75" customHeight="1">
       <c r="B30" s="7" t="s">
         <v>17</v>
       </c>
@@ -1772,7 +1767,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="15.75" customHeight="1">
       <c r="B31" s="7" t="s">
         <v>18</v>
       </c>
@@ -1780,31 +1775,31 @@
         <v>33</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="15.75" customHeight="1">
       <c r="B32" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C32" s="9">
+      <c r="C32" s="8">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="15.75" customHeight="1">
       <c r="B33" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C33" s="10" t="s">
+      <c r="C33" s="9" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="15.75" customHeight="1">
       <c r="B34" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C34" s="10" t="s">
+      <c r="C34" s="9" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="15.75" customHeight="1">
       <c r="B35" s="7" t="s">
         <v>24</v>
       </c>
@@ -1812,7 +1807,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="15.75" customHeight="1">
       <c r="B36" s="7" t="s">
         <v>26</v>
       </c>
@@ -1820,20 +1815,21 @@
         <v>27</v>
       </c>
     </row>
-    <row r="38">
+    <row r="37" ht="15.75" customHeight="1"/>
+    <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="7" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="15.75" customHeight="1">
       <c r="B39" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C39" s="8" t="s">
+      <c r="C39" s="7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="15.75" customHeight="1">
       <c r="B40" s="7" t="s">
         <v>14</v>
       </c>
@@ -1841,7 +1837,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="15.75" customHeight="1">
       <c r="B41" s="7" t="s">
         <v>2</v>
       </c>
@@ -1849,13 +1845,13 @@
         <v>1.0</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="15.75" customHeight="1">
       <c r="B42" s="7" t="s">
         <v>17</v>
       </c>
       <c r="C42" s="4"/>
     </row>
-    <row r="43">
+    <row r="43" ht="15.75" customHeight="1">
       <c r="B43" s="7" t="s">
         <v>18</v>
       </c>
@@ -1863,36 +1859,37 @@
         <v>36</v>
       </c>
     </row>
-    <row r="44">
-      <c r="B44" s="11" t="s">
+    <row r="44" ht="15.75" customHeight="1">
+      <c r="B44" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C44" s="12" t="s">
+      <c r="C44" s="11" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="45">
-      <c r="B45" s="13" t="s">
+    <row r="45" ht="15.75" customHeight="1">
+      <c r="B45" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="C45" s="14" t="s">
+      <c r="C45" s="13" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="47">
+    <row r="46" ht="15.75" customHeight="1"/>
+    <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="7" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" ht="15.75" customHeight="1">
       <c r="B48" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C48" s="8" t="s">
+      <c r="C48" s="7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" ht="15.75" customHeight="1">
       <c r="B49" s="7" t="s">
         <v>14</v>
       </c>
@@ -1900,7 +1897,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" ht="15.75" customHeight="1">
       <c r="B50" s="7" t="s">
         <v>2</v>
       </c>
@@ -1908,13 +1905,13 @@
         <v>1.0</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" ht="15.75" customHeight="1">
       <c r="B51" s="7" t="s">
         <v>17</v>
       </c>
       <c r="C51" s="4"/>
     </row>
-    <row r="52">
+    <row r="52" ht="15.75" customHeight="1">
       <c r="B52" s="7" t="s">
         <v>18</v>
       </c>
@@ -1922,36 +1919,37 @@
         <v>42</v>
       </c>
     </row>
-    <row r="53">
-      <c r="B53" s="11" t="s">
+    <row r="53" ht="15.75" customHeight="1">
+      <c r="B53" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C53" s="12" t="s">
+      <c r="C53" s="11" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="54">
-      <c r="B54" s="13" t="s">
+    <row r="54" ht="15.75" customHeight="1">
+      <c r="B54" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="C54" s="14" t="s">
+      <c r="C54" s="13" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="56">
+    <row r="55" ht="15.75" customHeight="1"/>
+    <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="7" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" ht="15.75" customHeight="1">
       <c r="B57" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C57" s="8" t="s">
+      <c r="C57" s="7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" ht="15.75" customHeight="1">
       <c r="B58" s="7" t="s">
         <v>14</v>
       </c>
@@ -1959,7 +1957,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" ht="15.75" customHeight="1">
       <c r="B59" s="7" t="s">
         <v>2</v>
       </c>
@@ -1967,13 +1965,13 @@
         <v>1.0</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" ht="15.75" customHeight="1">
       <c r="B60" s="7" t="s">
         <v>17</v>
       </c>
       <c r="C60" s="4"/>
     </row>
-    <row r="61">
+    <row r="61" ht="15.75" customHeight="1">
       <c r="B61" s="7" t="s">
         <v>18</v>
       </c>
@@ -1981,19 +1979,19 @@
         <v>45</v>
       </c>
     </row>
-    <row r="62">
-      <c r="B62" s="11" t="s">
+    <row r="62" ht="15.75" customHeight="1">
+      <c r="B62" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C62" s="12" t="s">
+      <c r="C62" s="11" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="63">
-      <c r="B63" s="13" t="s">
+    <row r="63" ht="15.75" customHeight="1">
+      <c r="B63" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="C63" s="14" t="s">
+      <c r="C63" s="13" t="s">
         <v>47</v>
       </c>
     </row>
